--- a/data/2604 인프런 매출데이터 변환.xlsx
+++ b/data/2604 인프런 매출데이터 변환.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minion\Desktop\알라딘\알라딘아카데미 정산관련\26.04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B0AF7D-0AA8-482A-BCF7-4137E1F352C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53FE281-9140-4B2D-95C1-54C5D6C90C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26775" yWindow="1305" windowWidth="25350" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,51 +160,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김광석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>김학균,안승찬</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서승완</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0051A2"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
+    <t>서승완</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>김광석</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -212,7 +176,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,13 +221,6 @@
       <sz val="10"/>
       <color rgb="FF0051A2"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0051A2"/>
-      <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -350,10 +307,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -663,7 +620,7 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -1305,8 +1262,8 @@
       <c r="C21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>40</v>
+      <c r="D21" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>24</v>
@@ -1398,8 +1355,8 @@
       <c r="C24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>41</v>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>24</v>
@@ -1429,8 +1386,8 @@
       <c r="C25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>42</v>
+      <c r="D25" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>24</v>
